--- a/SensitivityAnalysis/LeaveOneOut/BinaryData_LR/loo.xlsx
+++ b/SensitivityAnalysis/LeaveOneOut/BinaryData_LR/loo.xlsx
@@ -12,12 +12,18 @@
     <sheet name="IS" r:id="rId6" sheetId="4"/>
     <sheet name="Hypertension" r:id="rId7" sheetId="5"/>
     <sheet name="T2DM" r:id="rId8" sheetId="6"/>
+    <sheet name="Sheet6" r:id="rId9" sheetId="7"/>
+    <sheet name="Sheet7" r:id="rId10" sheetId="8"/>
+    <sheet name="Sheet8" r:id="rId11" sheetId="9"/>
+    <sheet name="Sheet9" r:id="rId12" sheetId="10"/>
+    <sheet name="Sheet10" r:id="rId13" sheetId="11"/>
+    <sheet name="Sheet11" r:id="rId14" sheetId="12"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="22">
   <si>
     <t>SNPS</t>
   </si>
@@ -78,6 +84,12 @@
   <si>
     <t>rs80107551</t>
   </si>
+  <si>
+    <t>CI_LOW</t>
+  </si>
+  <si>
+    <t>CI_HIGH</t>
+  </si>
 </sst>
 </file>
 
@@ -311,6 +323,582 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.20689218703478277</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.47838758901489886</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.06460321494533336</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.13851806223475313</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.13527716107862248</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.2276409629377731</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.5693444514092345</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.11406252553368831</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.17433851452625584</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.19164061763700227</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.20667858997954752</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.6187941210913648</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.20543694113226973</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.21026302607745778</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.32563076370323435</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.17815270488726356</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.5270529672997989</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.17074755752527174</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.17801033796557925</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.31692362188614936</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.2186914397808297</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.49166906040804537</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.054286180846386006</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.13927429623837537</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.11636368047931173</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.17268631882140556</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.4796100875888066</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.13423744994599546</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1565937595752046</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2701286720448782</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.2009288803694027</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.4737920809817015</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.07193432024289609</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.13921591867974428</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1489389228142584</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.028037395135022437</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.11692864848303003</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.06085385821298515</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04535268027959571</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5364381592998023</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.009492262900087648</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.09998816585687562</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1189726916570509</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.055857361610695544</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8650592539288884</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.009487993526625212</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.15835960150087916</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.13938361444762873</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.07595490202768058</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9005899369234214</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.03905683817131218</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.16557845699085333</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.08746478064822895</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.06455184633650057</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.545148414633448</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.0330295451819353</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.12083160359368378</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05477251322981317</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.04479696857742269</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4609298855235858</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.014286275517063893</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.12285071933698766</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.09427816830285987</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05539002235710396</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7964675212398737</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.03147219786077976</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.12574601331693835</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.06280161759537882</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.048098885436815605</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5129038534757318</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5240574231601224</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.39243030736688816</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.6556845389533565</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06715669173124195</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.0212131366391994E-15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5850388893151838</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4193417192813648</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7507360593490027</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08453937246623416</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.506479209550185E-12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5388787361231897</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3392697188799296</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7384877533664498</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.10184133532819391</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.214129275511695E-7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4246744245930645</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2555143381692313</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5938345110168977</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08630616654277201</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.629819737141958E-7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5238858939936692</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3915483215230374</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6562234664643011</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0675191696278734</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8.555511612139227E-15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.49658586534253696</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.34780479227853206</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6453669384065419</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.07590871074694128</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.074923188137512E-11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5293929613792822</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.39708530330224645</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6617006194563179</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.06750390718216107</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.41999028770247E-15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -1269,4 +1857,580 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.4654131298615298</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.7682965028446587</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1.162529756878401</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1545323331546576</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.4733595218194662E-21</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.7200044856466303</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.8913820555367937</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.548626915756467</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0874375356582466</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.80387018303226E-86</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.5387129060775913</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.0459999630525867</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.0314258491025958</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.25881992702805895</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.7627146504397488E-9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.2088055634241714</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.3833598680379198</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1.0342512588104231</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08905831868048385</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.775204941619358E-42</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.4706603760528403</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.8070130774014226</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.134307674704258</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1716085210962155</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.0361419923657E-17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.3706955937583551</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.6980398041918667</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.0433513833248436</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1670123522619957</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.264986453310088E-16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.4597420351125565</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.7954150524329657</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.1240690177921473</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.17126174353082105</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.548608498908295E-17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5333080947801566</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3889818668301319</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.6776343227301813</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07363583058674729</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.404623307106774E-13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5958735907521258</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4141270462856767</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7776201352185748</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.09272782880941279</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.3096302480753184E-10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5813857295337035</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.36259751427990056</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8001739447875065</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.11162664043561374</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.9057219815846575E-7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4745445568816174</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2892430087963564</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6598461049668785</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.09454160616594949</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.182621661787489E-7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5339637926198407</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.38885208594958376</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6790754992900977</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07403658503584541</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.507068725071013E-13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.4809286871274021</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3178434590705673</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6440139151842369</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0832067490085892</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.473436961410531E-9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5352135568463624</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.39012842004381393</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6802986936489108</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.07402302898089208</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.816957562862425E-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5510020199787137</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.36782024770810806</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7341837922493193</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09346008789316612</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.733531630704509E-9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6147740887935784</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3784171705095115</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8511310070776453</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.12059026443064638</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.431868517267146E-7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.4497245083354056</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1685649441732015</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7308840724976098</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.14344875722561434</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0017180243970847159</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.44433464405389284</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.21677636447659182</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6718929236311939</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.11610116304964338</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.2964423887575467E-4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5636996581470517</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.38576301320581896</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7416363030882844</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.09078400252103713</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.324146430871134E-10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.517285362922433</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.29679339425943685</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7377773315854291</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.11249590237907967</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.260349366726865E-6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5530667754751515</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.34812923682822866</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7580043141220743</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1045599686974096</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.2267157014687618E-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/SensitivityAnalysis/LeaveOneOut/BinaryData_LR/loo.xlsx
+++ b/SensitivityAnalysis/LeaveOneOut/BinaryData_LR/loo.xlsx
@@ -18,12 +18,18 @@
     <sheet name="Sheet9" r:id="rId12" sheetId="10"/>
     <sheet name="Sheet10" r:id="rId13" sheetId="11"/>
     <sheet name="Sheet11" r:id="rId14" sheetId="12"/>
+    <sheet name="Sheet12" r:id="rId15" sheetId="13"/>
+    <sheet name="Sheet13" r:id="rId16" sheetId="14"/>
+    <sheet name="Sheet14" r:id="rId17" sheetId="15"/>
+    <sheet name="Sheet15" r:id="rId18" sheetId="16"/>
+    <sheet name="Sheet16" r:id="rId19" sheetId="17"/>
+    <sheet name="Sheet17" r:id="rId20" sheetId="18"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="22">
   <si>
     <t>SNPS</t>
   </si>
@@ -899,6 +905,1158 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.4654131298615298</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.7682965028446587</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1.162529756878401</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1545323331546576</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.4733595218194662E-21</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.7200044856466303</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.8913820555367937</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.548626915756467</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0874375356582466</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.80387018303226E-86</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.5387129060775913</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.0459999630525867</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.0314258491025958</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.25881992702805895</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.7627146504397488E-9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.2088055634241714</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.3833598680379198</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1.0342512588104231</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08905831868048385</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.775204941619358E-42</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.4706603760528403</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.8070130774014226</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.134307674704258</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1716085210962155</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.0361419923657E-17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.3706955937583551</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.6980398041918667</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.0433513833248436</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1670123522619957</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.264986453310088E-16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.4597420351125565</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.7954150524329657</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.1240690177921473</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.17126174353082105</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.548608498908295E-17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5333080947801566</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3889818668301319</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.6776343227301813</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07363583058674729</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.404623307106774E-13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5958735907521258</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4141270462856767</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7776201352185748</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.09272782880941279</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.3096302480753184E-10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5813857295337035</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.36259751427990056</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8001739447875065</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.11162664043561374</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.9057219815846575E-7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4745445568816174</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2892430087963564</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6598461049668785</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.09454160616594949</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.182621661787489E-7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5339637926198407</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.38885208594958376</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6790754992900977</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07403658503584541</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.507068725071013E-13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.4809286871274021</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3178434590705673</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6440139151842369</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0832067490085892</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.473436961410531E-9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5352135568463624</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.39012842004381393</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6802986936489108</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.07402302898089208</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.816957562862425E-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5510020199787137</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.36782024770810806</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7341837922493193</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09346008789316612</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.733531630704509E-9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6147740887935784</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3784171705095115</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8511310070776453</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.12059026443064638</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.431868517267146E-7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.4497245083354056</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1685649441732015</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7308840724976098</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.14344875722561434</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0017180243970847159</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.44433464405389284</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.21677636447659182</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6718929236311939</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.11610116304964338</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.2964423887575467E-4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5636996581470517</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.38576301320581896</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7416363030882844</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.09078400252103713</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.324146430871134E-10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.517285362922433</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.29679339425943685</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7377773315854291</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.11249590237907967</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.260349366726865E-6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5530667754751515</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.34812923682822866</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7580043141220743</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1045599686974096</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.2267157014687618E-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.20689218703478277</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.47838758901489886</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.06460321494533336</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.13851806223475313</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.13527716107862248</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.2276409629377731</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.5693444514092345</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.11406252553368831</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.17433851452625584</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.19164061763700227</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.20667858997954752</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.6187941210913648</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.20543694113226973</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.21026302607745778</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.32563076370323435</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.17815270488726356</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.5270529672997989</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.17074755752527174</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.17801033796557925</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.31692362188614936</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.2186914397808297</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.49166906040804537</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.054286180846386006</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.13927429623837537</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.11636368047931173</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.17268631882140556</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.4796100875888066</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.13423744994599546</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1565937595752046</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2701286720448782</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.2009288803694027</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.4737920809817015</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.07193432024289609</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.13921591867974428</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1489389228142584</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.028037395135022437</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.11692864848303003</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.06085385821298515</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04535268027959571</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5364381592998023</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.009492262900087648</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.09998816585687562</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1189726916570509</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.055857361610695544</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8650592539288884</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.009487993526625212</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.15835960150087916</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.13938361444762873</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.07595490202768058</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9005899369234214</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.03905683817131218</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.16557845699085333</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.08746478064822895</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.06455184633650057</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.545148414633448</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.0330295451819353</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.12083160359368378</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05477251322981317</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.04479696857742269</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4609298855235858</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.014286275517063893</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.12285071933698766</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.09427816830285987</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05539002235710396</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7964675212398737</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.03147219786077976</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.12574601331693835</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.06280161759537882</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.048098885436815605</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5129038534757318</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5240574231601224</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.39243030736688816</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.6556845389533565</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06715669173124195</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.0212131366391994E-15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5850388893151838</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4193417192813648</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7507360593490027</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08453937246623416</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.506479209550185E-12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5388787361231897</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3392697188799296</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7384877533664498</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.10184133532819391</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.214129275511695E-7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4246744245930645</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2555143381692313</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5938345110168977</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08630616654277201</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.629819737141958E-7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5238858939936692</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3915483215230374</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6562234664643011</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0675191696278734</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8.555511612139227E-15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.49658586534253696</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.34780479227853206</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6453669384065419</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.07590871074694128</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.074923188137512E-11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5293929613792822</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.39708530330224645</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6617006194563179</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.06750390718216107</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.41999028770247E-15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>

--- a/SensitivityAnalysis/LeaveOneOut/BinaryData_LR/loo.xlsx
+++ b/SensitivityAnalysis/LeaveOneOut/BinaryData_LR/loo.xlsx
@@ -24,12 +24,18 @@
     <sheet name="Sheet15" r:id="rId18" sheetId="16"/>
     <sheet name="Sheet16" r:id="rId19" sheetId="17"/>
     <sheet name="Sheet17" r:id="rId20" sheetId="18"/>
+    <sheet name="Sheet18" r:id="rId21" sheetId="19"/>
+    <sheet name="Sheet19" r:id="rId22" sheetId="20"/>
+    <sheet name="Sheet20" r:id="rId23" sheetId="21"/>
+    <sheet name="Sheet21" r:id="rId24" sheetId="22"/>
+    <sheet name="Sheet22" r:id="rId25" sheetId="23"/>
+    <sheet name="Sheet23" r:id="rId26" sheetId="24"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="22">
   <si>
     <t>SNPS</t>
   </si>
@@ -2057,6 +2063,198 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.4154598308652713</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.7215128161646582</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1.1094068455658843</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1561494822956056</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.2486236105487267E-19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.64932659674115</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.8508483485078788</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.447804844974421</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.10281722028914737</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.571460138063354E-58</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.4755928847301083</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.989168682646806</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.9620170868134107</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2620284683248457</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.7872979104388738E-8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.158198436538011</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.3250481152664046</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.9913487578096172</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08512738710632332</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.715526162356355E-42</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.4287521410256008</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.7598319807092748</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.0976723013419267</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.16891828555289487</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.714328126929021E-17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.3120125891845962</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.6187012279268824</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.00532395044231</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1564737952766766</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.078141171217165E-17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.4107634540130765</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.7522844775303552</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.0692424304957977</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.17424542016187694</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.660190619646391E-16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -2242,6 +2440,966 @@
       </c>
       <c r="G8" t="n">
         <v>4.816957562862425E-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5134829041057515</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3737921609071785</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.6531736473043245</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0712707873462107</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.81821895093654E-13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5688339587085498</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.39380018858104826</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7438677288360513</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08930294394260282</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.8938451530730925E-10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5533280618024836</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3426383388259946</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7640177847789726</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.10749475662065766</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.6399668242332564E-7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4508978823261861</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2739365705425413</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6278591941098309</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.09028638356308408</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.911533074448079E-7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5168080635299136</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.37575727752949295</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6578588495303342</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07196468673490851</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.89950977849213E-13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.459407573839914</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3035750032088076</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6152401444710204</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0795064135872992</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.548362890453875E-9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5159546724986857</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.37539846780565</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6565108771917213</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.07171234933318144</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.256094414826021E-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5250739605043107</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.32948249656870465</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7206654244399167</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09979156323245204</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.4272413169968993E-7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5783938731307413</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.31857309552877483</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8382146507327077</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.13256162122549311</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.2816921144435164E-5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.4150970647487206</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1180207666502272</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.712173362847214</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1515695398461701</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.006169059416729137</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4145868795126799</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.19719860356508434</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6319751554602755</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.11091238568754877</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.8551401019393883E-4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5440135132685996</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3707110468743835</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7173159796628157</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.08841962571133476</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7.620698125990957E-10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.48613189473599067</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.25761354797484604</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7146502414971353</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.11659099324548196</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.0520258755960105E-5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.527672744649065</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.30882262666850036</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7465228626296296</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.11165822345947174</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.292282149826998E-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.19553556701701993</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.458329306350825</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.06725817231678513</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.13407843843561484</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.14473941777014127</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.21160713380906285</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.5407567039857338</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.11754243636760817</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.16793345417177094</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2076457734486787</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.18831881791809232</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.5853177770717785</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.20868014123559384</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2025504893641256</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.35250693074846</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.16353344180135768</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.49676432950477434</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.169697445902059</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.17001575903235547</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3361137762256622</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.2117749783505315</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.4771333030369754</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.053583346335912385</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.13538690035022646</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.11776577131191868</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.16117551573341254</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.45446619618452955</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.13211516471770446</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.14963810227097807</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2814346504236994</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.18939543376865825</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.4537472371617719</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0749563696244554</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1348733690781192</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.16024550953313021</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.02257439748884069</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.10962617214715019</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.06447737716946882</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04441417074403546</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6112638965987098</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.015829102050983927</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.08886749016485142</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.12052569426681926</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.053416628681548645</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7669758978572851</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0011206913114236217</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.14256846730750253</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.14480984993034976</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.07331079521373783</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9878033314625257</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.02961616975349831</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.15248914674615974</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0932568072391631</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.06269029438401093</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6366267938752364</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.029123910532057335</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.11549146550470629</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05724364444059163</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.044065079067678044</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5086575286330213</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.008767365665511732</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.11301968346526547</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.09548495213424202</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05318995806109885</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8690768303270344</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.026158940376355785</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.11878026392749548</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.06646238317478391</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04725577732201005</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5798795397698908</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.503953099076472</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3765337575968436</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.6313724405561004</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06500986810185125</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9.049364642008986E-15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5575443185255927</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3979280477923164</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.717160589258869</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08143687282310016</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.576460248638735E-12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5113504332265761</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.30235576501109035</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7203451014420619</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.10662993276300295</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.6221954002073756E-6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4035921770842913</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.24201730492454177</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5651670492440408</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08243615926517833</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.789918255948161E-7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5061292270146405</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.36700178700528713</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6452566670239939</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07098338775987416</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.0018754371655128E-12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.47218906650040854</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3299990059202339</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6143791270805832</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.07254594927559929</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.573965651453441E-11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.510010171184277</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.38140652163164823</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6386138207369059</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.06561410691460655</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.672518660134324E-15</v>
       </c>
     </row>
   </sheetData>

--- a/SensitivityAnalysis/LeaveOneOut/BinaryData_LR/loo.xlsx
+++ b/SensitivityAnalysis/LeaveOneOut/BinaryData_LR/loo.xlsx
@@ -30,12 +30,18 @@
     <sheet name="Sheet21" r:id="rId24" sheetId="22"/>
     <sheet name="Sheet22" r:id="rId25" sheetId="23"/>
     <sheet name="Sheet23" r:id="rId26" sheetId="24"/>
+    <sheet name="Sheet24" r:id="rId27" sheetId="25"/>
+    <sheet name="Sheet25" r:id="rId28" sheetId="26"/>
+    <sheet name="Sheet26" r:id="rId29" sheetId="27"/>
+    <sheet name="Sheet27" r:id="rId30" sheetId="28"/>
+    <sheet name="Sheet28" r:id="rId31" sheetId="29"/>
+    <sheet name="Sheet29" r:id="rId32" sheetId="30"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="22">
   <si>
     <t>SNPS</t>
   </si>
@@ -3407,6 +3413,966 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.4654131298615298</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.7682965028446587</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1.162529756878401</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1545323331546576</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.4733595218194662E-21</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.7200044856466303</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.8913820555367937</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.548626915756467</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0874375356582466</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.80387018303226E-86</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.5387129060775913</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.0459999630525867</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.0314258491025958</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.25881992702805895</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.7627146504397488E-9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.2088055634241714</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.3833598680379198</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1.0342512588104231</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08905831868048385</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.775204941619358E-42</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.4706603760528403</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.8070130774014226</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.134307674704258</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1716085210962155</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.0361419923657E-17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.3706955937583551</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.6980398041918667</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.0433513833248436</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1670123522619957</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.264986453310088E-16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.4597420351125565</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.7954150524329657</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.1240690177921473</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.17126174353082105</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.548608498908295E-17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5333080947801566</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3889818668301319</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.6776343227301813</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07363583058674729</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.404623307106774E-13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5958735907521258</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4141270462856767</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7776201352185748</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.09272782880941279</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.3096302480753184E-10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5813857295337035</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.36259751427990056</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8001739447875065</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.11162664043561374</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.9057219815846575E-7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4745445568816174</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2892430087963564</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6598461049668785</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.09454160616594949</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.182621661787489E-7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5339637926198407</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.38885208594958376</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6790754992900977</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07403658503584541</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.507068725071013E-13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.4809286871274021</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3178434590705673</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6440139151842369</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0832067490085892</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.473436961410531E-9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5352135568463624</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.39012842004381393</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6802986936489108</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.07402302898089208</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.816957562862425E-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5510020199787137</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.36782024770810806</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7341837922493193</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09346008789316612</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.733531630704509E-9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6147740887935784</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3784171705095115</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8511310070776453</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.12059026443064638</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.431868517267146E-7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.4497245083354056</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1685649441732015</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7308840724976098</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.14344875722561434</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0017180243970847159</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.44433464405389284</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.21677636447659182</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6718929236311939</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.11610116304964338</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.2964423887575467E-4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5636996581470517</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.38576301320581896</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7416363030882844</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.09078400252103713</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.324146430871134E-10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.517285362922433</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.29679339425943685</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7377773315854291</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.11249590237907967</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.260349366726865E-6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5530667754751515</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.34812923682822866</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7580043141220743</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1045599686974096</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.2267157014687618E-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.20689218703478277</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.47838758901489886</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.06460321494533336</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.13851806223475313</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.13527716107862248</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.2276409629377731</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.5693444514092345</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.11406252553368831</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.17433851452625584</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.19164061763700227</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.20667858997954752</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.6187941210913648</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.20543694113226973</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.21026302607745778</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.32563076370323435</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.17815270488726356</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.5270529672997989</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.17074755752527174</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.17801033796557925</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.31692362188614936</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.2186914397808297</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.49166906040804537</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.054286180846386006</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.13927429623837537</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.11636368047931173</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.17268631882140556</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.4796100875888066</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.13423744994599546</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1565937595752046</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2701286720448782</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.2009288803694027</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.4737920809817015</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.07193432024289609</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.13921591867974428</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1489389228142584</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.028037395135022437</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.11692864848303003</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.06085385821298515</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04535268027959571</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5364381592998023</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.009492262900087648</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.09998816585687562</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1189726916570509</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.055857361610695544</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8650592539288884</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.009487993526625212</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.15835960150087916</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.13938361444762873</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.07595490202768058</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9005899369234214</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.03905683817131218</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.16557845699085333</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.08746478064822895</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.06455184633650057</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.545148414633448</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.0330295451819353</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.12083160359368378</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05477251322981317</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.04479696857742269</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4609298855235858</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.014286275517063893</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.12285071933698766</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.09427816830285987</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05539002235710396</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7964675212398737</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.03147219786077976</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.12574601331693835</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.06280161759537882</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.048098885436815605</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5129038534757318</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -3592,6 +4558,198 @@
       </c>
       <c r="G8" t="n">
         <v>1.2267157014687618E-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5240574231601224</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.39243030736688816</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.6556845389533565</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06715669173124195</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.0212131366391994E-15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5850388893151838</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4193417192813648</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7507360593490027</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08453937246623416</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.506479209550185E-12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5388787361231897</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3392697188799296</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7384877533664498</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.10184133532819391</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.214129275511695E-7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4246744245930645</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2555143381692313</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5938345110168977</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08630616654277201</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.629819737141958E-7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5238858939936692</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3915483215230374</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6562234664643011</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0675191696278734</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8.555511612139227E-15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.49658586534253696</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.34780479227853206</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6453669384065419</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.07590871074694128</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.074923188137512E-11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5293929613792822</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.39708530330224645</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6617006194563179</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.06750390718216107</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.41999028770247E-15</v>
       </c>
     </row>
   </sheetData>
